--- a/artfynd/A 30076-2026 artfynd.xlsx
+++ b/artfynd/A 30076-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129120140</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6888453</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1010,6 +1025,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54026235</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1117,8 +1137,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60012744</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 30076-2026 artfynd.xlsx
+++ b/artfynd/A 30076-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ5"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1140,6 +1140,134 @@
       <c r="AZ5" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/60012744</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>135838522</v>
+      </c>
+      <c r="B6" t="n">
+        <v>101483</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Bealelund, Ög</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>537221</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6464996</v>
+      </c>
+      <c r="S6" t="n">
+        <v>72</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Skeda</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Gunilla Rech</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Gunilla Rech</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135838522</t>
         </is>
       </c>
     </row>
@@ -1149,6 +1277,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 30076-2026 artfynd.xlsx
+++ b/artfynd/A 30076-2026 artfynd.xlsx
@@ -1148,7 +1148,7 @@
         <v>135838522</v>
       </c>
       <c r="B6" t="n">
-        <v>101483</v>
+        <v>101485</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 30076-2026 artfynd.xlsx
+++ b/artfynd/A 30076-2026 artfynd.xlsx
@@ -1148,7 +1148,7 @@
         <v>135838522</v>
       </c>
       <c r="B6" t="n">
-        <v>101485</v>
+        <v>101502</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 30076-2026 artfynd.xlsx
+++ b/artfynd/A 30076-2026 artfynd.xlsx
@@ -1148,7 +1148,7 @@
         <v>135838522</v>
       </c>
       <c r="B6" t="n">
-        <v>101502</v>
+        <v>101504</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 30076-2026 artfynd.xlsx
+++ b/artfynd/A 30076-2026 artfynd.xlsx
@@ -1148,7 +1148,7 @@
         <v>135838522</v>
       </c>
       <c r="B6" t="n">
-        <v>101504</v>
+        <v>101505</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 30076-2026 artfynd.xlsx
+++ b/artfynd/A 30076-2026 artfynd.xlsx
@@ -1148,7 +1148,7 @@
         <v>135838522</v>
       </c>
       <c r="B6" t="n">
-        <v>101505</v>
+        <v>101506</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 30076-2026 artfynd.xlsx
+++ b/artfynd/A 30076-2026 artfynd.xlsx
@@ -1148,7 +1148,7 @@
         <v>135838522</v>
       </c>
       <c r="B6" t="n">
-        <v>101506</v>
+        <v>101512</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 30076-2026 artfynd.xlsx
+++ b/artfynd/A 30076-2026 artfynd.xlsx
@@ -1148,7 +1148,7 @@
         <v>135838522</v>
       </c>
       <c r="B6" t="n">
-        <v>101512</v>
+        <v>101513</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
